--- a/AHMRV/01_ERS/anexos/AnexoA_auditoria_calidad.xlsx
+++ b/AHMRV/01_ERS/anexos/AnexoA_auditoria_calidad.xlsx
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E8" s="40" t="inlineStr">
         <is>
-          <t>Cumple en ambos sentidos, sin requisitos huérfanos</t>
+          <t>Cumple en ambos sentidos sobre los 42 RF (denominador de esta métrica); los 19 RNF y 10 RD se verifican por otra vía, ver 04_Trazabilidad/readme.md</t>
         </is>
       </c>
     </row>
